--- a/data/trans_orig/P16A05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2007 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>12061</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11350</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28737</t>
+          <t>27708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15373</t>
+          <t>15622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33702</t>
+          <t>34739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,51%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260603</t>
+          <t>260949</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270373</t>
+          <t>270443</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>232101</t>
+          <t>233130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>249488</t>
+          <t>250249</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>500146</t>
+          <t>499109</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518475</t>
+          <t>518226</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6602</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19446</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>23514</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46083</t>
+          <t>46748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34237</t>
+          <t>32971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60985</t>
+          <t>60260</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>472887</t>
+          <t>473629</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486294</t>
+          <t>486473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457866</t>
+          <t>457201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480564</t>
+          <t>480435</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936039</t>
+          <t>936764</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>962787</t>
+          <t>964053</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15066</t>
+          <t>14240</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306907</t>
+          <t>306553</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316729</t>
+          <t>316680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330056</t>
+          <t>330021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639192</t>
+          <t>640018</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651244</t>
+          <t>651317</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11554</t>
+          <t>11555</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22966</t>
+          <t>22917</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>11694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29463</t>
+          <t>29726</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347117</t>
+          <t>347116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357614</t>
+          <t>357620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348490</t>
+          <t>348539</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362925</t>
+          <t>362731</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700664</t>
+          <t>700401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718172</t>
+          <t>718433</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1751</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25367</t>
+          <t>26077</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>192976</t>
+          <t>193020</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>202325</t>
+          <t>201557</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>188023</t>
+          <t>187344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201032</t>
+          <t>201244</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>385609</t>
+          <t>384899</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400715</t>
+          <t>400345</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6524</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19348</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264287</t>
+          <t>264338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261736</t>
+          <t>260834</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>274039</t>
+          <t>273604</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529588</t>
+          <t>529607</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>542964</t>
+          <t>543720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26475</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>36185</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63152</t>
+          <t>63671</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>588552</t>
+          <t>589368</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605744</t>
+          <t>605410</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>593935</t>
+          <t>595096</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>616083</t>
+          <t>616047</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1190094</t>
+          <t>1189575</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1216680</t>
+          <t>1217061</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23699</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46959</t>
+          <t>46293</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47608</t>
+          <t>46405</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>78095</t>
+          <t>75699</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>75831</t>
+          <t>75185</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>113118</t>
+          <t>112448</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>695818</t>
+          <t>696484</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>719078</t>
+          <t>720120</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>705416</t>
+          <t>707812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>735903</t>
+          <t>737106</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1413170</t>
+          <t>1413840</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1450457</t>
+          <t>1451103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>68210</t>
+          <t>67807</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>105061</t>
+          <t>103312</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>155861</t>
+          <t>155481</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207406</t>
+          <t>207452</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>235596</t>
+          <t>233080</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>301929</t>
+          <t>297133</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3170464</t>
+          <t>3172213</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3207315</t>
+          <t>3207718</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3171791</t>
+          <t>3171745</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3223336</t>
+          <t>3223716</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6352793</t>
+          <t>6357589</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6419126</t>
+          <t>6421642</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,5%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2012 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>10952</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29615</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15448</t>
+          <t>15608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34721</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>30463</t>
+          <t>29541</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56840</t>
+          <t>57384</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262580</t>
+          <t>262050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281392</t>
+          <t>281243</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>245591</t>
+          <t>246366</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264864</t>
+          <t>264704</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515666</t>
+          <t>515122</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>542043</t>
+          <t>542965</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,84%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9910</t>
+          <t>10265</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32467</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31538</t>
+          <t>31897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58872</t>
+          <t>58551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47830</t>
+          <t>48001</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81393</t>
+          <t>81161</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473060</t>
+          <t>473051</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495617</t>
+          <t>495262</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>463859</t>
+          <t>464180</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491193</t>
+          <t>490834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>946865</t>
+          <t>947097</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>980428</t>
+          <t>980257</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6718</t>
+          <t>5917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23044</t>
+          <t>22372</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4054</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>15615</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>11374</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>33103</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300072</t>
+          <t>300744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316398</t>
+          <t>317199</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325174</t>
+          <t>325405</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336966</t>
+          <t>336943</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631033</t>
+          <t>631921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651897</t>
+          <t>652762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3289</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>17708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29439</t>
+          <t>29308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>52739</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36108</t>
+          <t>35568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>64073</t>
+          <t>62049</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>355470</t>
+          <t>356274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370258</t>
+          <t>370693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>334371</t>
+          <t>335235</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358535</t>
+          <t>358666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>697883</t>
+          <t>699907</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>725848</t>
+          <t>726388</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24771</t>
+          <t>24335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>46909</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31852</t>
+          <t>31698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57030</t>
+          <t>57524</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196158</t>
+          <t>196180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208438</t>
+          <t>209224</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172201</t>
+          <t>172682</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194820</t>
+          <t>195256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375179</t>
+          <t>374685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400357</t>
+          <t>400511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,67%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8274</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24014</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14418</t>
+          <t>14514</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35271</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,04%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260411</t>
+          <t>260010</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270993</t>
+          <t>270896</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>255126</t>
+          <t>253740</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270979</t>
+          <t>270866</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>517850</t>
+          <t>519686</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538703</t>
+          <t>538607</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31988</t>
+          <t>31722</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19620</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>41986</t>
+          <t>40722</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36290</t>
+          <t>35988</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67751</t>
+          <t>66621</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630800</t>
+          <t>631066</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650474</t>
+          <t>650758</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>651867</t>
+          <t>653131</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>674233</t>
+          <t>674871</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1288890</t>
+          <t>1290020</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1320351</t>
+          <t>1320653</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12673</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32350</t>
+          <t>34167</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44560</t>
+          <t>44793</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>74868</t>
+          <t>75818</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62792</t>
+          <t>62880</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99149</t>
+          <t>99712</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>744622</t>
+          <t>742805</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764299</t>
+          <t>764020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>747802</t>
+          <t>746852</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>778110</t>
+          <t>777877</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1500493</t>
+          <t>1499930</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1536850</t>
+          <t>1536762</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>92671</t>
+          <t>94380</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>137543</t>
+          <t>141186</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>225291</t>
+          <t>220617</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>283634</t>
+          <t>285627</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>329798</t>
+          <t>329289</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>410502</t>
+          <t>410329</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3283636</t>
+          <t>3279993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3328508</t>
+          <t>3326799</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3263658</t>
+          <t>3261665</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3322001</t>
+          <t>3326675</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6557969</t>
+          <t>6558142</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6638673</t>
+          <t>6639182</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5429</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>18890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11880</t>
+          <t>12356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29636</t>
+          <t>31491</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42896</t>
+          <t>41930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274207</t>
+          <t>274871</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288332</t>
+          <t>288198</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>259067</t>
+          <t>257212</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276823</t>
+          <t>276347</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>539568</t>
+          <t>540534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>563068</t>
+          <t>562387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8608</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25491</t>
+          <t>25076</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26253</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>50955</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40091</t>
+          <t>39873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68286</t>
+          <t>69319</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477084</t>
+          <t>477499</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493967</t>
+          <t>493878</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472316</t>
+          <t>472129</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>497099</t>
+          <t>496831</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>957373</t>
+          <t>956340</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>985568</t>
+          <t>985786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17586</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27998</t>
+          <t>28066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19924</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40913</t>
+          <t>40866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300979</t>
+          <t>300491</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313446</t>
+          <t>313564</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308311</t>
+          <t>308243</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324404</t>
+          <t>324752</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613961</t>
+          <t>614008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>634950</t>
+          <t>635518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,04%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9360</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26085</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>45237</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36499</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65520</t>
+          <t>63401</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>343879</t>
+          <t>344764</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360604</t>
+          <t>360770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>341600</t>
+          <t>342046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364031</t>
+          <t>365190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>691727</t>
+          <t>693846</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>720748</t>
+          <t>721078</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,22%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4867</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16586</t>
+          <t>16231</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>40051</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27709</t>
+          <t>26924</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>51038</t>
+          <t>50881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,84%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194635</t>
+          <t>194990</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206606</t>
+          <t>206354</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>177239</t>
+          <t>178536</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>198746</t>
+          <t>199258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,08%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378770</t>
+          <t>378927</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>402099</t>
+          <t>402884</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,74%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>16522</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>14887</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>34226</t>
+          <t>35742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246173</t>
+          <t>246601</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259410</t>
+          <t>259360</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>249920</t>
+          <t>250069</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>265153</t>
+          <t>264557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>502012</t>
+          <t>500496</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521637</t>
+          <t>521351</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,22%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15080</t>
+          <t>14468</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35761</t>
+          <t>34660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>36309</t>
+          <t>37324</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66501</t>
+          <t>67884</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57612</t>
+          <t>55846</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92020</t>
+          <t>90454</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>620797</t>
+          <t>621898</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>641478</t>
+          <t>642090</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>624793</t>
+          <t>623410</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>654985</t>
+          <t>653970</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1255832</t>
+          <t>1257398</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1290240</t>
+          <t>1292006</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>16164</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>36158</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53098</t>
+          <t>53885</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>86787</t>
+          <t>87804</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74933</t>
+          <t>75592</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116265</t>
+          <t>115638</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>740678</t>
+          <t>742425</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762193</t>
+          <t>762419</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>739380</t>
+          <t>738363</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>773069</t>
+          <t>772282</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1488485</t>
+          <t>1489112</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1529817</t>
+          <t>1529158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100365</t>
+          <t>97572</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>144005</t>
+          <t>140507</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>238343</t>
+          <t>240366</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>303133</t>
+          <t>304472</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>348475</t>
+          <t>350080</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>426976</t>
+          <t>429092</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3250345</t>
+          <t>3253843</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3293985</t>
+          <t>3296778</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3241409</t>
+          <t>3240070</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3306199</t>
+          <t>3304176</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6511916</t>
+          <t>6509800</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6590417</t>
+          <t>6588812</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,95%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023</t>
+          <t>Población que ha consumido tranquilizantes en las dos últimas semanas en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4361</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>17124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16012</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13351</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>28740</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295368</t>
+          <t>294319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307359</t>
+          <t>307082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273623</t>
+          <t>273241</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282632</t>
+          <t>282393</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572070</t>
+          <t>572337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587726</t>
+          <t>587129</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>47593</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39285</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>61138</t>
+          <t>62469</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67245</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100603</t>
+          <t>97912</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469614</t>
+          <t>469800</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>496060</t>
+          <t>495978</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>452587</t>
+          <t>451256</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474440</t>
+          <t>474216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>930515</t>
+          <t>933206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>963873</t>
+          <t>964125</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,5%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8549</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23434</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>20147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35017</t>
+          <t>35402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33029</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>54667</t>
+          <t>51080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>292126</t>
+          <t>293377</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>306845</t>
+          <t>307011</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314111</t>
+          <t>313726</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329530</t>
+          <t>328981</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>610021</t>
+          <t>613608</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631659</t>
+          <t>632968</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,23%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16681</t>
+          <t>16418</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8357</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24312</t>
+          <t>24095</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15126</t>
+          <t>13728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34306</t>
+          <t>34012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>295876</t>
+          <t>296139</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309664</t>
+          <t>308953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>451075</t>
+          <t>451292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>467030</t>
+          <t>466698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>753638</t>
+          <t>753932</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>772818</t>
+          <t>774216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,26%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>17230</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27491</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20700</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32941</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>170130</t>
+          <t>169713</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176360</t>
+          <t>176501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>181165</t>
+          <t>180828</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191304</t>
+          <t>191426</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>354457</t>
+          <t>353189</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>366698</t>
+          <t>365790</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,42%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>21183</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>21665</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35030</t>
+          <t>36127</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33643</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52797</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>249055</t>
+          <t>248453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260934</t>
+          <t>260765</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>222026</t>
+          <t>220929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235852</t>
+          <t>235391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>473895</t>
+          <t>474982</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>493049</t>
+          <t>494129</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15576</t>
+          <t>15308</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32820</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>26207</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>83493</t>
+          <t>84891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103583</t>
+          <t>103064</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>591459</t>
+          <t>590772</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608703</t>
+          <t>608971</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>765154</t>
+          <t>763756</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>818572</t>
+          <t>822440</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1369343</t>
+          <t>1369862</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1420866</t>
+          <t>1419862</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,4%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>16971</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>53994</t>
+          <t>54901</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65234</t>
+          <t>65829</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98884</t>
+          <t>97647</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72953</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>143048</t>
+          <t>145481</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>874726</t>
+          <t>873819</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>914448</t>
+          <t>911749</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>615967</t>
+          <t>617204</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>649617</t>
+          <t>649022</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1500524</t>
+          <t>1498091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1570619</t>
+          <t>1575467</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,86%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>111138</t>
+          <t>114257</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169391</t>
+          <t>169604</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,7 +13461,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>231360</t>
+          <t>240418</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>325044</t>
+          <t>327373</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>376179</t>
+          <t>373970</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>481945</t>
+          <t>479385</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3288939</t>
+          <t>3288726</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3347192</t>
+          <t>3344073</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13579,7 +13579,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3332040</t>
+          <t>3329711</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3425724</t>
+          <t>3416666</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6633469</t>
+          <t>6636029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6739235</t>
+          <t>6741444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P16A05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P16A05-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12061</t>
+          <t>12199</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10589</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27708</t>
+          <t>26701</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34739</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>260949</t>
+          <t>260811</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270443</t>
+          <t>270429</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>233130</t>
+          <t>234137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>250249</t>
+          <t>250337</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>499109</t>
+          <t>497250</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>518226</t>
+          <t>517320</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6602</t>
+          <t>6287</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>20308</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23514</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46748</t>
+          <t>45278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32971</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60260</t>
+          <t>59736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473629</t>
+          <t>472767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>486473</t>
+          <t>486788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>457201</t>
+          <t>458671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>480435</t>
+          <t>480781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>936764</t>
+          <t>937288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>964053</t>
+          <t>962832</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2166</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12293</t>
+          <t>12428</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14240</t>
+          <t>13086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>306553</t>
+          <t>306418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>316680</t>
+          <t>315950</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330021</t>
+          <t>330168</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640018</t>
+          <t>641172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651317</t>
+          <t>651322</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8725</t>
+          <t>8351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>22967</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>11441</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29726</t>
+          <t>29692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347116</t>
+          <t>346582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>357620</t>
+          <t>357608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348539</t>
+          <t>348489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>362731</t>
+          <t>363105</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>700401</t>
+          <t>700435</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>718433</t>
+          <t>718686</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1751</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>9440</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6424</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20324</t>
+          <t>20715</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26077</t>
+          <t>26267</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>193020</t>
+          <t>193868</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>201557</t>
+          <t>201544</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187344</t>
+          <t>186953</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201244</t>
+          <t>201006</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>384899</t>
+          <t>384709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400345</t>
+          <t>400990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>6068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19348</t>
+          <t>19432</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264338</t>
+          <t>264130</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260834</t>
+          <t>261779</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273604</t>
+          <t>273895</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>529607</t>
+          <t>529523</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>543720</t>
+          <t>542887</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9404</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>25659</t>
+          <t>26010</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22172</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36185</t>
+          <t>35057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>63671</t>
+          <t>62032</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>589368</t>
+          <t>589017</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>605410</t>
+          <t>605623</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>595096</t>
+          <t>592793</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>616047</t>
+          <t>615514</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1189575</t>
+          <t>1191214</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1217061</t>
+          <t>1218189</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22657</t>
+          <t>22974</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>46293</t>
+          <t>46236</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>46405</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75699</t>
+          <t>78022</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>75185</t>
+          <t>75214</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>112448</t>
+          <t>113860</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>696484</t>
+          <t>696541</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>720120</t>
+          <t>719803</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>707812</t>
+          <t>705489</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>737106</t>
+          <t>738630</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1413840</t>
+          <t>1412428</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1451103</t>
+          <t>1451074</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>67807</t>
+          <t>69233</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>103312</t>
+          <t>104896</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>155481</t>
+          <t>153029</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>207452</t>
+          <t>205573</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>233080</t>
+          <t>232017</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>297133</t>
+          <t>294823</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3172213</t>
+          <t>3170629</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3207718</t>
+          <t>3206292</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3171745</t>
+          <t>3173624</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3223716</t>
+          <t>3226168</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6357589</t>
+          <t>6359899</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6421642</t>
+          <t>6422705</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,51%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10952</t>
+          <t>10844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30145</t>
+          <t>28749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15608</t>
+          <t>15141</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33946</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>31207</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57384</t>
+          <t>58565</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>262050</t>
+          <t>263446</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>281243</t>
+          <t>281351</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>246366</t>
+          <t>244601</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>264704</t>
+          <t>265171</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>515122</t>
+          <t>513941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>542965</t>
+          <t>541299</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10265</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32476</t>
+          <t>32315</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31897</t>
+          <t>31159</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58551</t>
+          <t>58566</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48001</t>
+          <t>48054</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81161</t>
+          <t>81431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>473051</t>
+          <t>473212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495262</t>
+          <t>495354</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464180</t>
+          <t>464165</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>490834</t>
+          <t>491572</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>947097</t>
+          <t>946827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>980257</t>
+          <t>980204</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22372</t>
+          <t>22296</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15615</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11374</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>32065</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300744</t>
+          <t>300820</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317199</t>
+          <t>317135</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>325405</t>
+          <t>325533</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>336943</t>
+          <t>336989</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>631921</t>
+          <t>632071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>652762</t>
+          <t>651764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,14%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>4125</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29308</t>
+          <t>29740</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52739</t>
+          <t>53785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35568</t>
+          <t>35677</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62049</t>
+          <t>64760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>356274</t>
+          <t>355711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>370693</t>
+          <t>369857</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335235</t>
+          <t>334189</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>358666</t>
+          <t>358234</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,41%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>699907</t>
+          <t>697196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>726388</t>
+          <t>726279</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24335</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46909</t>
+          <t>46893</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31698</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>57524</t>
+          <t>55522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>196180</t>
+          <t>196223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>209224</t>
+          <t>208547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>172682</t>
+          <t>172698</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>195256</t>
+          <t>195132</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374685</t>
+          <t>376687</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>400511</t>
+          <t>400499</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13971</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25400</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14059</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33435</t>
+          <t>33825</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260010</t>
+          <t>259520</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270896</t>
+          <t>270982</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>253740</t>
+          <t>255035</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>270866</t>
+          <t>270370</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>519686</t>
+          <t>519296</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>538607</t>
+          <t>539062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12030</t>
+          <t>12672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>31722</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18982</t>
+          <t>19178</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40722</t>
+          <t>40048</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35988</t>
+          <t>34974</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>66621</t>
+          <t>63553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>631066</t>
+          <t>631127</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650758</t>
+          <t>650116</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>653131</t>
+          <t>653805</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>674871</t>
+          <t>674675</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1290020</t>
+          <t>1293088</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1320653</t>
+          <t>1321667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>11741</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>34167</t>
+          <t>33660</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44793</t>
+          <t>43781</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75818</t>
+          <t>73938</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>62880</t>
+          <t>63903</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>99712</t>
+          <t>99910</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742805</t>
+          <t>743312</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>764020</t>
+          <t>765231</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>746852</t>
+          <t>748732</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>777877</t>
+          <t>778889</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1499930</t>
+          <t>1499732</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1536762</t>
+          <t>1535739</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,01%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>94380</t>
+          <t>91134</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>141186</t>
+          <t>138415</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>220617</t>
+          <t>222140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>285627</t>
+          <t>287276</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>329289</t>
+          <t>330772</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>410329</t>
+          <t>412982</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,93%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3279993</t>
+          <t>3282764</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3326799</t>
+          <t>3330045</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3261665</t>
+          <t>3260016</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3326675</t>
+          <t>3325152</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6558142</t>
+          <t>6555489</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6639182</t>
+          <t>6637699</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>5149</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12356</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31491</t>
+          <t>29912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20007</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41930</t>
+          <t>41978</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>274871</t>
+          <t>275500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>288198</t>
+          <t>288612</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257212</t>
+          <t>258791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>276347</t>
+          <t>276599</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>540534</t>
+          <t>540486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>562387</t>
+          <t>562457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,57%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8697</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25076</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26253</t>
+          <t>26465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50955</t>
+          <t>49712</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>41213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69319</t>
+          <t>69552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>477499</t>
+          <t>476932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493878</t>
+          <t>493124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>472129</t>
+          <t>473372</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>496831</t>
+          <t>496619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>956340</t>
+          <t>956107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>985786</t>
+          <t>984446</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28066</t>
+          <t>28475</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>20146</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40866</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>300491</t>
+          <t>300573</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313564</t>
+          <t>313858</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308243</t>
+          <t>307834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324752</t>
+          <t>323938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>614008</t>
+          <t>614463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>635518</t>
+          <t>634728</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>9180</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25200</t>
+          <t>25247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22093</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45237</t>
+          <t>44961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36169</t>
+          <t>36491</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63401</t>
+          <t>64577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>344764</t>
+          <t>344717</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>360770</t>
+          <t>360784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>342046</t>
+          <t>342322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>365190</t>
+          <t>364865</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>693846</t>
+          <t>692670</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>721078</t>
+          <t>720756</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4867</t>
+          <t>4793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16231</t>
+          <t>17313</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>20121</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40051</t>
+          <t>40089</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26661</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50881</t>
+          <t>49888</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>194990</t>
+          <t>193908</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>206354</t>
+          <t>206428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178536</t>
+          <t>178498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199258</t>
+          <t>198466</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>378927</t>
+          <t>379920</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>402884</t>
+          <t>403147</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16522</t>
+          <t>16528</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8112</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23046</t>
+          <t>22752</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14887</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>35742</t>
+          <t>35149</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>246601</t>
+          <t>246595</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>259360</t>
+          <t>259246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>250069</t>
+          <t>250363</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>264557</t>
+          <t>265003</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>500496</t>
+          <t>501089</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>521351</t>
+          <t>521071</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14468</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34660</t>
+          <t>33123</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37324</t>
+          <t>37733</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67884</t>
+          <t>66536</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55846</t>
+          <t>56191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90454</t>
+          <t>91676</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>621898</t>
+          <t>623435</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>642090</t>
+          <t>641987</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>623410</t>
+          <t>624758</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>653970</t>
+          <t>653561</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1257398</t>
+          <t>1256176</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1292006</t>
+          <t>1291661</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16164</t>
+          <t>16496</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>36158</t>
+          <t>37146</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53885</t>
+          <t>53893</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87804</t>
+          <t>87488</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>75592</t>
+          <t>75819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115638</t>
+          <t>117190</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>742425</t>
+          <t>741437</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>762419</t>
+          <t>762087</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>738363</t>
+          <t>738679</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>772282</t>
+          <t>772274</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1489112</t>
+          <t>1487560</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1529158</t>
+          <t>1528931</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,28%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>97572</t>
+          <t>99860</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140507</t>
+          <t>142104</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>240366</t>
+          <t>240175</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>304472</t>
+          <t>304450</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>350080</t>
+          <t>347022</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>429092</t>
+          <t>426620</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3253843</t>
+          <t>3252246</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3296778</t>
+          <t>3294490</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3240070</t>
+          <t>3240092</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3304176</t>
+          <t>3304367</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6509800</t>
+          <t>6512272</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6588812</t>
+          <t>6591870</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8777</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4361</t>
+          <t>3872</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17124</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7242</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>20086</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28740</t>
+          <t>28605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>302666</t>
+          <t>310432</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>294319</t>
+          <t>303996</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>307082</t>
+          <t>314973</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>278615</t>
+          <t>304388</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273241</t>
+          <t>298640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282393</t>
+          <t>308241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>581280</t>
+          <t>614820</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>572337</t>
+          <t>606301</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>587129</t>
+          <t>620883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32024</t>
+          <t>32424</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21415</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47593</t>
+          <t>47471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50447</t>
+          <t>52005</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39509</t>
+          <t>41518</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62469</t>
+          <t>63624</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>82471</t>
+          <t>84429</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66993</t>
+          <t>68735</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>97912</t>
+          <t>102875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>485369</t>
+          <t>497236</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469800</t>
+          <t>482189</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495978</t>
+          <t>507598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>463278</t>
+          <t>493208</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>451256</t>
+          <t>481589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>474216</t>
+          <t>503695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>948647</t>
+          <t>990444</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933206</t>
+          <t>971998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>964125</t>
+          <t>1006138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517393</t>
+          <t>529660</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513725</t>
+          <t>545213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031118</t>
+          <t>1074873</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>14500</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8549</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22183</t>
+          <t>22228</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>26887</t>
+          <t>27127</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20147</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>36074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41387</t>
+          <t>41304</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31720</t>
+          <t>33018</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51080</t>
+          <t>53058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>301060</t>
+          <t>301321</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>293377</t>
+          <t>293270</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>307011</t>
+          <t>306908</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>322241</t>
+          <t>329254</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>313726</t>
+          <t>320307</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328981</t>
+          <t>336242</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>623301</t>
+          <t>630576</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613608</t>
+          <t>618822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632968</t>
+          <t>638862</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315560</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664688</t>
+          <t>671880</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,27 +11726,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3604</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16418</t>
+          <t>19588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>16510</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8689</t>
+          <t>11224</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24095</t>
+          <t>24945</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13728</t>
+          <t>16620</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -11839,22 +11839,22 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>304733</t>
+          <t>364904</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296139</t>
+          <t>353557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>308953</t>
+          <t>369537</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>460391</t>
+          <t>405120</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>451292</t>
+          <t>396685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466698</t>
+          <t>410406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>765124</t>
+          <t>770024</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>753932</t>
+          <t>758730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>774216</t>
+          <t>778155</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,91%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475387</t>
+          <t>421630</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787944</t>
+          <t>794775</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4790</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9029</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>21874</t>
+          <t>22923</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17230</t>
+          <t>17759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27828</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21608</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>35457</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>173952</t>
+          <t>200619</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>169713</t>
+          <t>195255</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>176501</t>
+          <t>203296</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>186782</t>
+          <t>204292</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>180828</t>
+          <t>198380</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191426</t>
+          <t>209456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>360733</t>
+          <t>404910</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>353189</t>
+          <t>397422</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365790</t>
+          <t>411555</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21183</t>
+          <t>21186</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>28214</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21665</t>
+          <t>21963</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36127</t>
+          <t>36130</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>41732</t>
+          <t>41837</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>33727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51710</t>
+          <t>51223</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>255688</t>
+          <t>257084</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248453</t>
+          <t>249521</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260765</t>
+          <t>262078</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>229272</t>
+          <t>235536</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>220929</t>
+          <t>227620</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235391</t>
+          <t>241787</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>484960</t>
+          <t>492620</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>474982</t>
+          <t>483234</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>494129</t>
+          <t>500730</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,69%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>23384</t>
+          <t>27424</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15308</t>
+          <t>18619</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33507</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>59236</t>
+          <t>70380</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26207</t>
+          <t>56635</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84891</t>
+          <t>85807</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>82621</t>
+          <t>97804</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>53064</t>
+          <t>81211</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>103064</t>
+          <t>116931</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>600895</t>
+          <t>692263</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>590772</t>
+          <t>680033</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>608971</t>
+          <t>701068</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>789411</t>
+          <t>700999</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>763756</t>
+          <t>685572</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>822440</t>
+          <t>714744</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1390305</t>
+          <t>1393262</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1369862</t>
+          <t>1374135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1419862</t>
+          <t>1409855</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>848647</t>
+          <t>771379</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>848647</t>
+          <t>771379</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>848647</t>
+          <t>771379</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1472926</t>
+          <t>1491066</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1472926</t>
+          <t>1491066</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1472926</t>
+          <t>1491066</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>36466</t>
+          <t>41093</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>16971</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54901</t>
+          <t>54269</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>78643</t>
+          <t>85254</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>65829</t>
+          <t>71791</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97647</t>
+          <t>99657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>115110</t>
+          <t>126347</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>68105</t>
+          <t>109299</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>145481</t>
+          <t>145834</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>892254</t>
+          <t>756979</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>873819</t>
+          <t>743803</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>911749</t>
+          <t>767645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>636208</t>
+          <t>744752</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>617204</t>
+          <t>730349</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>649022</t>
+          <t>758215</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1528462</t>
+          <t>1501731</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1498091</t>
+          <t>1482244</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1575467</t>
+          <t>1518779</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714851</t>
+          <t>830006</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643572</t>
+          <t>1628078</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>141714</t>
+          <t>150440</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>114257</t>
+          <t>128724</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>169604</t>
+          <t>176451</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>290887</t>
+          <t>314087</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>240418</t>
+          <t>288698</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>327373</t>
+          <t>344031</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>432601</t>
+          <t>464527</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>373970</t>
+          <t>428107</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>479385</t>
+          <t>501395</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3316616</t>
+          <t>3380840</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3288726</t>
+          <t>3354829</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3344073</t>
+          <t>3402556</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3366197</t>
+          <t>3417548</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3329711</t>
+          <t>3387604</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3416666</t>
+          <t>3442937</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6682813</t>
+          <t>6798388</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6636029</t>
+          <t>6761520</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6741444</t>
+          <t>6834808</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,11%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458330</t>
+          <t>3531280</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3657084</t>
+          <t>3731635</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7115414</t>
+          <t>7262915</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
